--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1559,110 +1559,6 @@
   </si>
   <si>
     <t>{Request that resulted in Event in activity.performedActivity}</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.extension:artRegimenSwitchedOrSubstituted</t>
-  </si>
-  <si>
-    <t>artRegimenSwitchedOrSubstituted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/art-regimen-switched-or-substituted}
-</t>
-  </si>
-  <si>
-    <t>ART Regimen Switched Or Substituted</t>
-  </si>
-  <si>
-    <t>The ARV regimen has been switched to a new ARV regimen or has been substituted by another ARV regimen.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t>ref-2
-ref-1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient") - must be a resource in resources</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a known RESTful URL) or by resolving the target of the reference.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).
-This element only allows for a single identifier. In the case where additional identifers are required, use the [http://hl7.org/fhir/StructureDefinition/additionalIdentifier](http://hl7.org/fhir/extensions/StructureDefinition-additionalIdentifier.html) extension.</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-2
-</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>CarePlan.note</t>
@@ -2002,12 +1898,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="82.83984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="32.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="47.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.95703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2015,7 +1911,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.05078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.99609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -7985,7 +7881,7 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>462</v>
@@ -8675,7 +8571,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>495</v>
@@ -8706,10 +8602,10 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -8718,16 +8614,18 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>90</v>
+        <v>482</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>164</v>
+        <v>497</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>165</v>
+        <v>498</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8775,833 +8673,35 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>166</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>168</v>
+        <v>487</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AN66" t="s" s="2">
         <v>488</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN66">
+  <autoFilter ref="A1:AN59">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9611,7 +8711,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -495,7 +495,7 @@
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -495,7 +495,7 @@
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
     <t>Slice based on the type of identifier.</t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -559,9 +559,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3518,10 +3515,10 @@
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3550,10 +3547,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3579,16 +3576,16 @@
         <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3616,28 +3613,28 @@
         <v>112</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3658,7 +3655,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>133</v>
@@ -3666,10 +3663,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3692,19 +3689,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3729,31 +3726,31 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3774,18 +3771,18 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3894,10 +3891,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3976,10 +3973,10 @@
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4008,10 +4005,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4034,19 +4031,19 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4095,7 +4092,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4116,18 +4113,18 @@
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4236,10 +4233,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4318,10 +4315,10 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4350,10 +4347,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4379,16 +4376,16 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4398,46 +4395,46 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4458,18 +4455,18 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4492,16 +4489,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4551,7 +4548,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4572,18 +4569,18 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4609,14 +4606,14 @@
         <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4665,7 +4662,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4674,7 +4671,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4686,18 +4683,18 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4720,17 +4717,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4740,46 +4737,46 @@
         <v>80</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4788,7 +4785,7 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
@@ -4800,18 +4797,18 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4834,19 +4831,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4895,7 +4892,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4916,18 +4913,18 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4950,19 +4947,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4972,46 +4969,46 @@
         <v>80</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5032,18 +5029,18 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5069,65 +5066,65 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T28" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T28" t="s" s="2">
+      <c r="U28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5148,18 +5145,18 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5182,16 +5179,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5205,43 +5202,43 @@
         <v>80</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5250,7 +5247,7 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -5262,18 +5259,18 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5296,13 +5293,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5353,7 +5350,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5374,18 +5371,18 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5408,16 +5405,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5467,7 +5464,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5488,18 +5485,18 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5522,13 +5519,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5579,7 +5576,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5594,13 +5591,13 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5608,10 +5605,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5637,13 +5634,13 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5693,7 +5690,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5708,13 +5705,13 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5722,14 +5719,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5748,17 +5745,17 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5807,7 +5804,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5822,7 +5819,7 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -5836,14 +5833,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5862,19 +5859,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5923,7 +5920,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5938,7 +5935,7 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5952,10 +5949,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5978,16 +5975,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6037,7 +6034,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6066,10 +6063,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6095,16 +6092,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6132,10 +6129,10 @@
         <v>112</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6153,7 +6150,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6168,24 +6165,24 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6211,16 +6208,16 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6248,11 +6245,11 @@
         <v>112</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6269,7 +6266,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -6284,7 +6281,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
@@ -6298,10 +6295,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6324,19 +6321,19 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6361,14 +6358,14 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6385,7 +6382,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6403,7 +6400,7 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6414,10 +6411,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6440,13 +6437,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6497,7 +6494,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6526,10 +6523,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6552,17 +6549,17 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6611,7 +6608,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6629,7 +6626,7 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6640,14 +6637,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6666,13 +6663,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6723,7 +6720,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>88</v>
@@ -6738,24 +6735,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6778,16 +6775,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6837,7 +6834,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6852,28 +6849,28 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6892,19 +6889,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6953,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6968,28 +6965,28 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7008,13 +7005,13 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7065,7 +7062,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7080,13 +7077,13 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7094,10 +7091,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7120,16 +7117,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7179,7 +7176,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7194,10 +7191,10 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7208,10 +7205,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7234,16 +7231,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7293,7 +7290,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7322,10 +7319,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7348,17 +7345,17 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7404,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7422,10 +7419,10 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7436,10 +7433,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7462,19 +7459,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7499,14 +7496,14 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7523,7 +7520,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7538,24 +7535,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>441</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7578,19 +7575,19 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7639,7 +7636,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7654,7 +7651,7 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>80</v>
@@ -7668,10 +7665,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7694,19 +7691,19 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7755,7 +7752,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7776,18 +7773,18 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7810,17 +7807,17 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7869,7 +7866,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7884,13 +7881,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7898,10 +7895,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7924,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>164</v>
@@ -8010,10 +8007,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8095,7 +8092,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8124,14 +8121,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8153,10 +8150,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8211,7 +8208,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8240,10 +8237,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8266,19 +8263,19 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8303,14 +8300,14 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8327,7 +8324,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8342,13 +8339,13 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8356,10 +8353,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8382,19 +8379,19 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8443,7 +8440,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8464,18 +8461,18 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8498,19 +8495,19 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8559,7 +8556,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8574,13 +8571,13 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8588,10 +8585,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8614,17 +8611,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8673,7 +8670,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8688,16 +8685,16 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
